--- a/ingredients.xlsx
+++ b/ingredients.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>Ingredient</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>BAR Cocoa Powder</t>
+  </si>
+  <si>
+    <t>Amul Taaza Tetrapack</t>
   </si>
 </sst>
 </file>
@@ -480,7 +483,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="29.29"/>
+    <col customWidth="1" min="1" max="1" width="25.71"/>
     <col customWidth="1" min="2" max="2" width="33.14"/>
     <col customWidth="1" min="3" max="3" width="12.29"/>
     <col customWidth="1" min="4" max="4" width="10.29"/>
@@ -1309,25 +1312,25 @@
         <v>40</v>
       </c>
       <c r="C18" s="5">
-        <v>587.0</v>
+        <v>600.0</v>
       </c>
       <c r="D18" s="5">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E18" s="5">
-        <v>50.3</v>
+        <v>51.0</v>
       </c>
       <c r="F18" s="5">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
       <c r="G18" s="5">
-        <v>39.7</v>
+        <v>37.0</v>
       </c>
       <c r="H18" s="4">
         <v>0.0</v>
       </c>
       <c r="I18" s="5">
-        <v>34.0</v>
+        <v>30.0</v>
       </c>
       <c r="J18" s="4">
         <v>0.0</v>
@@ -1345,7 +1348,7 @@
         <v>100.0</v>
       </c>
       <c r="O18" s="5">
-        <v>200.0</v>
+        <v>195.0</v>
       </c>
     </row>
     <row r="19">
@@ -1459,7 +1462,53 @@
         <v>200.0</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="5">
+        <v>58.0</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="F21" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="G21" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>37.0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>110.0</v>
+      </c>
+      <c r="K21" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="L21" s="5">
+        <v>88.5</v>
+      </c>
+      <c r="M21" s="5">
+        <v>100.0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>16.0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>7.5</v>
+      </c>
+    </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>

--- a/ingredients.xlsx
+++ b/ingredients.xlsx
@@ -16,10 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
-  <si>
-    <t>Ingredient</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>Name</t>
   </si>
@@ -148,6 +145,18 @@
   </si>
   <si>
     <t>Amul Taaza Tetrapack</t>
+  </si>
+  <si>
+    <t>Mix-in</t>
+  </si>
+  <si>
+    <t>Strawberry</t>
+  </si>
+  <si>
+    <t>Hazelnut Paste</t>
+  </si>
+  <si>
+    <t>Vanilla Bean</t>
   </si>
 </sst>
 </file>
@@ -495,63 +504,62 @@
     <col customWidth="1" min="10" max="10" width="12.43"/>
     <col customWidth="1" min="11" max="11" width="9.57"/>
     <col customWidth="1" min="12" max="12" width="9.71"/>
-    <col customWidth="1" min="13" max="15" width="6.71"/>
+    <col customWidth="1" min="13" max="14" width="7.0"/>
+    <col customWidth="1" min="15" max="15" width="6.71"/>
     <col customWidth="1" min="16" max="29" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="C2" s="4">
         <v>355.55</v>
@@ -595,10 +603,10 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="C3" s="4">
         <v>62.0</v>
@@ -642,10 +650,10 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="4">
         <v>91.0</v>
@@ -689,10 +697,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="4">
         <v>63.0</v>
@@ -736,10 +744,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="4">
         <v>86.0</v>
@@ -783,10 +791,10 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="C7" s="4">
         <v>367.0</v>
@@ -830,10 +838,10 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="C8" s="4">
         <v>558.0</v>
@@ -877,10 +885,10 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="C9" s="4">
         <v>387.0</v>
@@ -924,10 +932,10 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="4">
         <v>350.0</v>
@@ -971,10 +979,10 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>31</v>
       </c>
       <c r="C11" s="4">
         <v>714.0</v>
@@ -1018,10 +1026,10 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4">
         <v>208.0</v>
@@ -1065,10 +1073,10 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C13" s="4">
         <v>387.0</v>
@@ -1112,10 +1120,10 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="5">
         <v>64.7</v>
@@ -1160,10 +1168,10 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5">
         <v>538.0</v>
@@ -1209,10 +1217,10 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="5">
         <v>551.0</v>
@@ -1259,10 +1267,10 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="C17" s="5">
         <v>409.0</v>
@@ -1306,10 +1314,10 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="5">
         <v>600.0</v>
@@ -1353,10 +1361,10 @@
     </row>
     <row r="19">
       <c r="A19" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" s="14">
         <v>560.0</v>
@@ -1417,10 +1425,10 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5">
         <v>313.0</v>
@@ -1464,10 +1472,10 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="5">
         <v>58.0</v>
@@ -1509,9 +1517,149 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="5">
+        <v>32.0</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="E22" s="5">
+        <v>7.7</v>
+      </c>
+      <c r="F22" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="K22" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>90.0</v>
+      </c>
+      <c r="M22" s="9">
+        <f>((2.4*190)+(2*180)+(0.4*100))/4.8</f>
+        <v>178.3333333</v>
+      </c>
+      <c r="N22" s="9">
+        <f>((2.4*175)+(2*72.5)+(0.4*100))/4.8</f>
+        <v>126.0416667</v>
+      </c>
+      <c r="O22" s="5">
+        <v>45.0</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="5">
+        <v>580.0</v>
+      </c>
+      <c r="D23" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="E23" s="5">
+        <v>25.8</v>
+      </c>
+      <c r="F23" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G23" s="5">
+        <v>50.6</v>
+      </c>
+      <c r="H23" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="5">
+        <v>300.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="5">
+        <v>5000.0</v>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>

--- a/ingredients.xlsx
+++ b/ingredients.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
   <si>
     <t>Name</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>Vanilla Bean</t>
+  </si>
+  <si>
+    <t>Lemon Juice</t>
   </si>
 </sst>
 </file>
@@ -1660,7 +1663,53 @@
         <v>5000.0</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J25" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>90.0</v>
+      </c>
+      <c r="M25" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="5">
+        <v>120.0</v>
+      </c>
+    </row>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>

--- a/ingredients.xlsx
+++ b/ingredients.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>Name</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>Lemon Juice</t>
+  </si>
+  <si>
+    <t>BAR33 White Couverture</t>
   </si>
 </sst>
 </file>
@@ -224,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -274,9 +277,6 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1404,27 +1404,27 @@
         <f>((46*100)+(5*100))/51</f>
         <v>100</v>
       </c>
-      <c r="N19" s="17">
-        <f>((46*100)+(5*16))/51</f>
-        <v>91.76470588</v>
+      <c r="N19" s="16">
+        <f>((46*100)+(1*16))/47</f>
+        <v>98.21276596</v>
       </c>
       <c r="O19" s="14">
         <v>145.0</v>
       </c>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="18"/>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="18"/>
-      <c r="AC19" s="18"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
@@ -1710,7 +1710,56 @@
         <v>120.0</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="14">
+        <v>570.0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>7.0</v>
+      </c>
+      <c r="E26" s="14">
+        <v>55.0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>45.0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>36.0</v>
+      </c>
+      <c r="H26" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="I26" s="14">
+        <v>0.0</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="16">
+        <f>1.07*(0.88*D26+6)</f>
+        <v>13.0112</v>
+      </c>
+      <c r="L26" s="15">
+        <v>0.0</v>
+      </c>
+      <c r="M26" s="16">
+        <f>((44*100)+(1*100))/45</f>
+        <v>100</v>
+      </c>
+      <c r="N26" s="16">
+        <f>((44*100)+(1*16))/45</f>
+        <v>98.13333333</v>
+      </c>
+      <c r="O26" s="14">
+        <v>145.0</v>
+      </c>
+    </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>

--- a/ingredients.xlsx
+++ b/ingredients.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -163,6 +163,12 @@
   </si>
   <si>
     <t>BAR33 White Couverture</t>
+  </si>
+  <si>
+    <t>Vanilla Essence</t>
+  </si>
+  <si>
+    <t>Mango Pulp</t>
   </si>
 </sst>
 </file>
@@ -1760,8 +1766,103 @@
         <v>145.0</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="5">
+        <v>370.0</v>
+      </c>
+      <c r="D27" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E27" s="5">
+        <v>88.0</v>
+      </c>
+      <c r="F27" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="G27" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="H27" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="M27" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="5">
+        <v>1000.0</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="5">
+        <v>60.0</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="E28" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="F28" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H28" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="J28" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="9">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="5">
+        <v>80.0</v>
+      </c>
+      <c r="M28" s="9">
+        <f>(0.4*100)+(0.3*190)+(0.3*180)</f>
+        <v>151</v>
+      </c>
+      <c r="N28" s="9">
+        <f>(0.4*100)+(0.3*170)+(0.3*70)</f>
+        <v>112</v>
+      </c>
+      <c r="O28" s="9">
+        <f>1300/(0.6*250*12)*100</f>
+        <v>72.22222222</v>
+      </c>
+    </row>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
